--- a/res/efficiency/pet-md/orca2-13b-Q4_K_S/2025-02-12_17-17-27/efficiency.xlsx
+++ b/res/efficiency/pet-md/orca2-13b-Q4_K_S/2025-02-12_17-17-27/efficiency.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Felix\Documents\GitHub\llm-process-generation\res\efficiency\pet-md\orca2-13b-Q4_K_S\2025-02-12_17-17-27\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Felix\Documents\llm-process-generation\res\efficiency\pet-md\orca2-13b-Q4_K_S\2025-02-12_17-17-27\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E0FC168-33E7-4D36-B686-519C6A642E19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C8B1BEF-6686-485A-B990-52370481499B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11520" yWindow="0" windowWidth="11520" windowHeight="12360" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Power_Stats" sheetId="1" r:id="rId1"/>
@@ -510,6 +510,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="14.109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
@@ -571,6 +575,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.77734375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
